--- a/Codes/Trial 3/Trial3_LSTM_Followers_Results.xlsx
+++ b/Codes/Trial 3/Trial3_LSTM_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         <v>2024</v>
       </c>
       <c r="C2" t="n">
-        <v>4.96</v>
+        <v>6.920000000000002</v>
       </c>
       <c r="D2" t="n">
-        <v>5.060079574584961</v>
+        <v>3.020319700241089</v>
       </c>
       <c r="E2" t="n">
-        <v>0.100079574584961</v>
+        <v>3.899680299758913</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>3.76</v>
+        <v>15.39</v>
       </c>
       <c r="D3" t="n">
-        <v>6.23805046081543</v>
+        <v>2.743055820465088</v>
       </c>
       <c r="E3" t="n">
-        <v>2.47805046081543</v>
+        <v>12.64694417953491</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>8.919999999999998</v>
+        <v>8.520000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>6.358756065368652</v>
+        <v>2.548848152160645</v>
       </c>
       <c r="E4" t="n">
-        <v>2.561243934631346</v>
+        <v>5.971151847839357</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>6.200000000000001</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>5.855687141418457</v>
+        <v>2.748731851577759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.344312858581544</v>
+        <v>4.901268148422241</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2024</v>
       </c>
       <c r="C6" t="n">
-        <v>6.920000000000002</v>
+        <v>28.37</v>
       </c>
       <c r="D6" t="n">
-        <v>4.769988536834717</v>
+        <v>2.922926664352417</v>
       </c>
       <c r="E6" t="n">
-        <v>2.150011463165285</v>
+        <v>25.44707333564758</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2024</v>
       </c>
       <c r="C7" t="n">
-        <v>15.39</v>
+        <v>39.77999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>4.880029201507568</v>
+        <v>2.819400072097778</v>
       </c>
       <c r="E7" t="n">
-        <v>10.50997079849243</v>
+        <v>36.96059992790222</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2024</v>
       </c>
       <c r="C8" t="n">
-        <v>8.520000000000001</v>
+        <v>3.34</v>
       </c>
       <c r="D8" t="n">
-        <v>5.476401329040527</v>
+        <v>3.057778835296631</v>
       </c>
       <c r="E8" t="n">
-        <v>3.043598670959474</v>
+        <v>0.282221164703369</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,111 +638,15 @@
         <v>2024</v>
       </c>
       <c r="C9" t="n">
-        <v>7.649999999999999</v>
+        <v>6.980000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>5.383557319641113</v>
+        <v>3.004782676696777</v>
       </c>
       <c r="E9" t="n">
-        <v>2.266442680358886</v>
+        <v>3.975217323303224</v>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5.353721618652344</v>
-      </c>
-      <c r="E10" t="n">
-        <v>23.01627838134766</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C11" t="n">
-        <v>39.77999999999999</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7.665345191955566</v>
-      </c>
-      <c r="E11" t="n">
-        <v>32.11465480804443</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.012363910675049</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.672363910675049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6.980000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.415323734283447</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.564676265716554</v>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
